--- a/examples/micro_workbooks/cross_sheet_taco_patterns.xlsx
+++ b/examples/micro_workbooks/cross_sheet_taco_patterns.xlsx
@@ -1,40 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sravan\excel-grapher\examples\micro_workbooks\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891B2D41-4AEE-4815-A9DB-9B052154152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Report" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>alpha</t>
   </si>
@@ -50,15 +31,12 @@
   <si>
     <t>epsilon</t>
   </si>
-  <si>
-    <t>Computed</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,21 +73,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,7 +117,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -181,7 +151,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -216,10 +185,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,11 +360,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B3:N11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14">
       <c r="B3">
         <v>2</v>
       </c>
@@ -416,7 +384,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>3</v>
       </c>
@@ -436,7 +404,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>4</v>
       </c>
@@ -456,7 +424,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>5</v>
       </c>
@@ -476,7 +444,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>6</v>
       </c>
@@ -496,22 +464,22 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14">
       <c r="E8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14">
       <c r="E9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14">
       <c r="E10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14">
       <c r="E11">
         <v>10</v>
       </c>
@@ -522,134 +490,113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C3:K8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="D3:K7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:11">
       <c r="D3">
         <f>Data!B3*Data!C3</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <f>SUM(Data!E3:'Data'!$E$11)</f>
-        <v>90</v>
+        <f>SUM(Data!E3:Data!$E$11)</f>
+        <v>0</v>
       </c>
       <c r="H3">
-        <f>SUM(Data!$G$3:'Data'!G3)</f>
-        <v>2</v>
+        <f>SUM(Data!$G$3:Data!G3)</f>
+        <v>0</v>
       </c>
       <c r="J3" t="s">
         <v>0</v>
       </c>
       <c r="K3">
-        <f>VLOOKUP(J3,Data!$M$3:'Data'!$N$7,2,FALSE)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.35">
+        <f>VLOOKUP(J3,Data!$M$3:Data!$N$7,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="4:11">
       <c r="D4">
         <f>Data!B4*Data!C4</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <f>SUM(Data!E4:'Data'!$E$11)</f>
-        <v>80</v>
+        <f>SUM(Data!E4:Data!$E$11)</f>
+        <v>0</v>
       </c>
       <c r="H4">
-        <f>SUM(Data!$G$3:'Data'!G4)</f>
-        <v>5</v>
+        <f>SUM(Data!$G$3:Data!G4)</f>
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
       </c>
       <c r="K4">
-        <f>VLOOKUP(J4,Data!$M$3:'Data'!$N$7,2,FALSE)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.35">
+        <f>VLOOKUP(J4,Data!$M$3:Data!$N$7,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="4:11">
       <c r="D5">
         <f>Data!B5*Data!C5</f>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <f>SUM(Data!E5:'Data'!$E$11)</f>
-        <v>70</v>
+        <f>SUM(Data!E5:Data!$E$11)</f>
+        <v>0</v>
       </c>
       <c r="H5">
-        <f>SUM(Data!$G$3:'Data'!G5)</f>
-        <v>9</v>
+        <f>SUM(Data!$G$3:Data!G5)</f>
+        <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
       </c>
       <c r="K5">
-        <f>VLOOKUP(J5,Data!$M$3:'Data'!$N$7,2,FALSE)</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.35">
+        <f>VLOOKUP(J5,Data!$M$3:Data!$N$7,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="4:11">
       <c r="D6">
         <f>Data!B6*Data!C6</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f>SUM(Data!E6:'Data'!$E$11)</f>
-        <v>60</v>
+        <f>SUM(Data!E6:Data!$E$11)</f>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f>SUM(Data!$G$3:'Data'!G6)</f>
-        <v>14</v>
+        <f>SUM(Data!$G$3:Data!G6)</f>
+        <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>3</v>
       </c>
       <c r="K6">
-        <f>VLOOKUP(J6,Data!$M$3:'Data'!$N$7,2,FALSE)</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.35">
+        <f>VLOOKUP(J6,Data!$M$3:Data!$N$7,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11">
       <c r="D7">
         <f>Data!B7*Data!C7</f>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <f>SUM(Data!E7:'Data'!$E$11)</f>
-        <v>50</v>
+        <f>SUM(Data!E7:Data!$E$11)</f>
+        <v>0</v>
       </c>
       <c r="H7">
-        <f>SUM(Data!$G$3:'Data'!G7)</f>
-        <v>20</v>
+        <f>SUM(Data!$G$3:Data!G7)</f>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <f>VLOOKUP(J7,Data!$M$3:'Data'!$N$7,2,FALSE)</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <f>AVERAGE(D3:D7)</f>
-        <v>180</v>
-      </c>
-      <c r="F8">
-        <f t="shared" ref="E8:K8" si="0">AVERAGE(F3:F7)</f>
-        <v>70</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <f>VLOOKUP(J7,Data!$M$3:Data!$N$7,2,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
